--- a/entrega/tabla-stride-cliente.xlsx
+++ b/entrega/tabla-stride-cliente.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,11 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +123,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1195,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1494,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1598,7 +1606,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1606,14 +1614,14 @@
           <t>Cabeceras de seguridad HTTP (HSTS, CSP, X-Frame-Options)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>curl -I sobre el portal público o securityheaders.com</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Pendiente de ejecutar y de registrar el resultado antes de la sustentación.</t>
+          <t>Verificado el 13/09/2026. securityheaders.com califica el portal con nota A. Presentes: Strict-Transport-Security (max-age=31536000; includeSubDomains), Content-Security-Policy completa, X-Frame-Options: SAMEORIGIN, X-Content-Type-Options: nosniff y Referrer-Policy. Falta Permissions-Policy (por eso queda en A y no A+).</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1621,14 +1629,14 @@
           <t>Tampering, Information Disclosure</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Por verificar</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Verificado por el equipo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1636,14 +1644,14 @@
           <t>Mensajes de error expuestos en el portal público</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Solicitud de una ruta inexistente y observación de la respuesta</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Pendiente de ejecutar; interesa saber si se devuelve una página genérica o una traza con versiones de software.</t>
+          <t>Verificado el 13/09/2026 con curl -I. El encabezado Server informa 'nginx' sin versión (correcto). Divulgación menor: la CSP expone nombres de entornos internos (unisabanastartdev/stage/prod, *.acquia-sites.com) e infraestructura (Acquia, CloudFront, Varnish, New Relic nr-spa-1.310.1). No se observaron trazas de error ni versiones sensibles de framework.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1651,9 +1659,9 @@
           <t>Information Disclosure</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Por verificar</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Verificado por el equipo</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1696,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1696,14 +1704,14 @@
           <t>Filtraciones históricas asociadas al dominio institucional</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Consulta del dominio en haveibeenpwned.com (solo lectura)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Pendiente de ejecutar; alimenta la probabilidad asignada a las amenazas de suplantación por credenciales.</t>
+          <t>Verificado el 13/09/2026 en haveibeenpwned.com. El correo institucional consultado no aparece en ninguna brecha cargada en el servicio (0 resultados). Reduce, sin eliminar, la probabilidad de las amenazas de suplantación por credenciales filtradas (C1).</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1711,9 +1719,9 @@
           <t>Spoofing, Information Disclosure</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Por verificar</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Verificado por el equipo</t>
         </is>
       </c>
     </row>
